--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123642227</v>
+        <v>123642201</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hack i träd</t>
+          <t>hack i granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123642201</v>
+        <v>123642227</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i granar</t>
+          <t>hack i träd</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123642201</v>
+        <v>123642227</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hack i granar</t>
+          <t>hack i träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123642227</v>
+        <v>123642201</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i träd</t>
+          <t>hack i granar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123642227</v>
+        <v>123642201</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hack i träd</t>
+          <t>hack i granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123642201</v>
+        <v>123642227</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i granar</t>
+          <t>hack i träd</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123642201</v>
+        <v>123642227</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hack i granar</t>
+          <t>hack i träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123642227</v>
+        <v>123642201</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i träd</t>
+          <t>hack i granar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123642227</v>
+        <v>123642201</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hack i träd</t>
+          <t>hack i granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123642201</v>
+        <v>123642227</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i granar</t>
+          <t>hack i träd</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124330157</v>
+        <v>124329003</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,31 +1161,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788209</v>
+        <v>788163</v>
       </c>
       <c r="R6" t="n">
-        <v>7113034</v>
+        <v>7113023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,17 +1230,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124330216</v>
+        <v>124330157</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1298,7 +1293,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1308,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788211</v>
+        <v>788209</v>
       </c>
       <c r="R7" t="n">
-        <v>7112990</v>
+        <v>7113034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1343,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124329003</v>
+        <v>124330216</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,30 +1496,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1532,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788163</v>
+        <v>788211</v>
       </c>
       <c r="R9" t="n">
-        <v>7113023</v>
+        <v>7112990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,13 +1566,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124329003</v>
+        <v>124330157</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,30 +1161,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788163</v>
+        <v>788209</v>
       </c>
       <c r="R6" t="n">
-        <v>7113023</v>
+        <v>7113034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,13 +1231,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124330157</v>
+        <v>124330085</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,35 +1272,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788209</v>
+        <v>788145</v>
       </c>
       <c r="R7" t="n">
-        <v>7113034</v>
+        <v>7113051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,17 +1345,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330085</v>
+        <v>124330216</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1382,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788145</v>
+        <v>788211</v>
       </c>
       <c r="R8" t="n">
-        <v>7113051</v>
+        <v>7112990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,13 +1456,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124330216</v>
+        <v>124329003</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,31 +1501,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1528,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788211</v>
+        <v>788163</v>
       </c>
       <c r="R9" t="n">
-        <v>7112990</v>
+        <v>7113023</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,17 +1570,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124330085</v>
+        <v>124330216</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,34 +1272,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788145</v>
+        <v>788211</v>
       </c>
       <c r="R7" t="n">
-        <v>7113051</v>
+        <v>7112990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,13 +1346,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330216</v>
+        <v>124330085</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,35 +1387,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788211</v>
+        <v>788145</v>
       </c>
       <c r="R8" t="n">
-        <v>7112990</v>
+        <v>7113051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,17 +1460,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hack i träd</t>
+          <t>barksprätt på gamla granar, troligen tretåig hackspett men det kan även vara andra hackspettar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124330157</v>
+        <v>124329003</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,31 +1161,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788209</v>
+        <v>788163</v>
       </c>
       <c r="R6" t="n">
-        <v>7113034</v>
+        <v>7113023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,17 +1230,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124330216</v>
+        <v>124330085</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,35 +1267,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788211</v>
+        <v>788145</v>
       </c>
       <c r="R7" t="n">
-        <v>7112990</v>
+        <v>7113051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,17 +1340,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330085</v>
+        <v>124330216</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,34 +1377,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1422,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788145</v>
+        <v>788211</v>
       </c>
       <c r="R8" t="n">
-        <v>7113051</v>
+        <v>7112990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,13 +1451,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1485,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124329003</v>
+        <v>124330157</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,30 +1496,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1532,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788163</v>
+        <v>788209</v>
       </c>
       <c r="R9" t="n">
-        <v>7113023</v>
+        <v>7113034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,13 +1566,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124330085</v>
+        <v>124330216</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1267,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788145</v>
+        <v>788211</v>
       </c>
       <c r="R7" t="n">
-        <v>7113051</v>
+        <v>7112990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,13 +1341,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330216</v>
+        <v>124330085</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,35 +1382,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788211</v>
+        <v>788145</v>
       </c>
       <c r="R8" t="n">
-        <v>7112990</v>
+        <v>7113051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,17 +1455,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124330216</v>
+        <v>124330085</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,35 +1267,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788211</v>
+        <v>788145</v>
       </c>
       <c r="R7" t="n">
-        <v>7112990</v>
+        <v>7113051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,17 +1340,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330085</v>
+        <v>124330216</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1377,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788145</v>
+        <v>788211</v>
       </c>
       <c r="R8" t="n">
-        <v>7113051</v>
+        <v>7112990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,13 +1451,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124329003</v>
+        <v>124330216</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,30 +1161,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788163</v>
+        <v>788211</v>
       </c>
       <c r="R6" t="n">
-        <v>7113023</v>
+        <v>7112990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,13 +1231,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330216</v>
+        <v>124329003</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,31 +1386,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788211</v>
+        <v>788163</v>
       </c>
       <c r="R8" t="n">
-        <v>7112990</v>
+        <v>7113023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,17 +1455,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124330216</v>
+        <v>124330085</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,35 +1157,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788211</v>
+        <v>788145</v>
       </c>
       <c r="R6" t="n">
-        <v>7112990</v>
+        <v>7113051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,17 +1230,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124330085</v>
+        <v>124329003</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,31 +1267,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788145</v>
+        <v>788163</v>
       </c>
       <c r="R7" t="n">
-        <v>7113051</v>
+        <v>7113023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124329003</v>
+        <v>124330216</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,30 +1381,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788163</v>
+        <v>788211</v>
       </c>
       <c r="R8" t="n">
-        <v>7113023</v>
+        <v>7112990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,13 +1451,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124329003</v>
+        <v>124330216</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,30 +1271,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788163</v>
+        <v>788211</v>
       </c>
       <c r="R7" t="n">
-        <v>7113023</v>
+        <v>7112990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,13 +1341,17 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330216</v>
+        <v>124329003</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,31 +1386,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788211</v>
+        <v>788163</v>
       </c>
       <c r="R8" t="n">
-        <v>7112990</v>
+        <v>7113023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,17 +1455,13 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124330085</v>
+        <v>124329003</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,31 +1157,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788145</v>
+        <v>788163</v>
       </c>
       <c r="R6" t="n">
-        <v>7113051</v>
+        <v>7113023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124329003</v>
+        <v>124330085</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,31 +1382,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788163</v>
+        <v>788145</v>
       </c>
       <c r="R8" t="n">
-        <v>7113023</v>
+        <v>7113051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124329003</v>
+        <v>124330085</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,31 +1157,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788163</v>
+        <v>788145</v>
       </c>
       <c r="R6" t="n">
-        <v>7113023</v>
+        <v>7113051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124330085</v>
+        <v>124329003</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,31 +1382,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788145</v>
+        <v>788163</v>
       </c>
       <c r="R8" t="n">
-        <v>7113051</v>
+        <v>7113023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>123642227</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>124330157</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 59868-2024 artfynd.xlsx
+++ b/artfynd/A 59868-2024 artfynd.xlsx
@@ -920,11 +920,6 @@
       <c r="B4" t="n">
         <v>57635</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1484,11 +1479,6 @@
       </c>
       <c r="B9" t="n">
         <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
